--- a/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67748_completo.xlsx
+++ b/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67748_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7a7dfd0e929b49c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R73e65474d42449e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    229.2891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    227.7779</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    240.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    295.2609</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    246.5078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    235.4242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    238.5459</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    230.8094</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    249.7557</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    273.5010</x:v>
+        <x:v>    270.0006</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67748_completo.xlsx
+++ b/49848_Cuenca_Huayabamba/_raw_reportes_xlsx/IDConfig_67748_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R73e65474d42449e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Ra43504c85dcb48ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    263.1081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    363.9654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    180.5657</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    182.9660</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    191.6509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    204.8245</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    230.8094</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.2648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    256.3598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    240.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    229.2891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    243.2960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    280.6100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    270.0006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    254.6952</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    235.4242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    271.7463</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    259.7159</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    246.5078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    263.1081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    314.3860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    463.2277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    284.2186</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    291.5441</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    342.6761</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    411.6082</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    191.6509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    186.6340</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    194.2135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    214.5826</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    233.8769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    238.5459</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    208.9524</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    189.1244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    194.2135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    190.3832</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    196.8122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    202.1177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    206.1915</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    207.5674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    220.3570</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    236.9805</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    256.3598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    286.0365</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    357.4840</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    521.5706</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    320.2994</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    314.3860</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    841.7721</x:v>
+        <x:v>    987.0925</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    664.0134</x:v>
+        <x:v>    777.4809</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    581.3329</x:v>
+        <x:v>    834.4843</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    805.6940</x:v>
+        <x:v>   1027.4989</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1481.1594</x:v>
+        <x:v>   1562.1134</x:v>
       </x:c>
     </x:row>
     <x:row>
